--- a/results/04_final_refined_daily_hydroclimate_data/501/Max_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/501/Max_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -428,7 +428,7 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>32.9</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -442,7 +442,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -456,7 +456,7 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -483,8 +483,8 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7">
-        <v>30.6</v>
+      <c r="D7" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>31.4</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -539,8 +539,8 @@
       <c r="C11">
         <v>10</v>
       </c>
-      <c r="D11" t="s">
-        <v>4</v>
+      <c r="D11">
+        <v>31.2</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -553,8 +553,8 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12" t="s">
-        <v>4</v>
+      <c r="D12">
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -581,8 +581,8 @@
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="D14" t="s">
-        <v>4</v>
+      <c r="D14">
+        <v>23.4</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -595,8 +595,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15" t="s">
-        <v>4</v>
+      <c r="D15">
+        <v>30.9</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -610,7 +610,7 @@
         <v>15</v>
       </c>
       <c r="D16">
-        <v>31.8</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -624,7 +624,7 @@
         <v>16</v>
       </c>
       <c r="D17">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -680,7 +680,7 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -722,7 +722,7 @@
         <v>23</v>
       </c>
       <c r="D24">
-        <v>30.8</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -749,8 +749,8 @@
       <c r="C26">
         <v>25</v>
       </c>
-      <c r="D26" t="s">
-        <v>4</v>
+      <c r="D26">
+        <v>25.8</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -763,8 +763,8 @@
       <c r="C27">
         <v>26</v>
       </c>
-      <c r="D27" t="s">
-        <v>4</v>
+      <c r="D27">
+        <v>29.2</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -792,7 +792,7 @@
         <v>28</v>
       </c>
       <c r="D29">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="30" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/501/Max_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/501/Max_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Year</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Max_Temperature</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -483,8 +480,8 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7" t="s">
-        <v>4</v>
+      <c r="D7">
+        <v>30.5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -497,8 +494,8 @@
       <c r="C8">
         <v>7</v>
       </c>
-      <c r="D8" t="s">
-        <v>4</v>
+      <c r="D8">
+        <v>31.1</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -540,7 +537,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -554,7 +551,7 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>33</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -624,7 +621,7 @@
         <v>16</v>
       </c>
       <c r="D17">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -680,7 +677,7 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -708,7 +705,7 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="24" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/501/Max_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/501/Max_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -26,6 +26,9 @@
   </si>
   <si>
     <t>Max_Temperature</t>
+  </si>
+  <si>
+    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -481,7 +484,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -565,7 +568,7 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -579,7 +582,7 @@
         <v>13</v>
       </c>
       <c r="D14">
-        <v>23.4</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -718,8 +721,8 @@
       <c r="C24">
         <v>23</v>
       </c>
-      <c r="D24">
-        <v>39.8</v>
+      <c r="D24" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -747,7 +750,7 @@
         <v>25</v>
       </c>
       <c r="D26">
-        <v>25.8</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -789,7 +792,7 @@
         <v>28</v>
       </c>
       <c r="D29">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -817,7 +820,7 @@
         <v>30</v>
       </c>
       <c r="D31">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -831,7 +834,7 @@
         <v>31</v>
       </c>
       <c r="D32">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
     </row>
   </sheetData>

--- a/results/04_final_refined_daily_hydroclimate_data/501/Max_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/501/Max_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Year</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Max_Temperature</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -484,7 +481,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -568,7 +565,7 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -582,7 +579,7 @@
         <v>13</v>
       </c>
       <c r="D14">
-        <v>31.4</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -721,8 +718,8 @@
       <c r="C24">
         <v>23</v>
       </c>
-      <c r="D24" t="s">
-        <v>4</v>
+      <c r="D24">
+        <v>39.8</v>
       </c>
     </row>
     <row r="25" spans="1:4">
